--- a/AI-Inventory-Waste-Manager-Technical.xlsx
+++ b/AI-Inventory-Waste-Manager-Technical.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{DB1CD0D2-C0E7-8D4E-BB69-51771DF97AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18260" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0. Roadmap" sheetId="1" r:id="rId1"/>
